--- a/申請書/第一申請書範本.xlsx
+++ b/申請書/第一申請書範本.xlsx
@@ -5,13 +5,13 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cfe2efa93682d330/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fbf32e69ea87f61e/Desktop/claude/申請書/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="623" documentId="8_{8657E013-8DDC-4972-BDBF-6C2620C0497F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42FD3C7F-7D1A-4DDF-BDCA-57E302D7C2A1}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="BwhljbYaKav+E17RuyDNCkx7FNkCIijIIhGeSyh/zEvLWC29IGnQmrBFwgnc+icxQOJkDEe40IlAn/u+KarW+w==" workbookSaltValue="AzwUdSEg380nYmyDCj3oGQ==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{1319B317-115B-4189-827F-8B258237D3A2}"/>
+    <workbookView xWindow="-1605" yWindow="945" windowWidth="17340" windowHeight="13485" xr2:uid="{1319B317-115B-4189-827F-8B258237D3A2}"/>
   </bookViews>
   <sheets>
     <sheet name="申請書" sheetId="1" r:id="rId1"/>
@@ -1052,6 +1052,150 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="5" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1062,14 +1206,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1086,18 +1222,6 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1130,132 +1254,8 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1463,10 +1463,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1781,63 +1777,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="25.5" customHeight="1">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
-      <c r="I1" s="62"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
-      <c r="T1" s="62"/>
-      <c r="U1" s="62"/>
-      <c r="V1" s="62"/>
-      <c r="W1" s="62"/>
-      <c r="X1" s="62"/>
-      <c r="Y1" s="62"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="40"/>
+      <c r="R1" s="40"/>
+      <c r="S1" s="40"/>
+      <c r="T1" s="40"/>
+      <c r="U1" s="40"/>
+      <c r="V1" s="40"/>
+      <c r="W1" s="40"/>
+      <c r="X1" s="40"/>
+      <c r="Y1" s="40"/>
       <c r="Z1" s="21"/>
     </row>
     <row r="2" spans="1:34" ht="25.5" customHeight="1">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="63"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="63"/>
-      <c r="K2" s="63"/>
-      <c r="L2" s="63"/>
-      <c r="M2" s="63"/>
-      <c r="N2" s="63"/>
-      <c r="O2" s="63"/>
-      <c r="P2" s="63"/>
-      <c r="Q2" s="63"/>
-      <c r="R2" s="63"/>
-      <c r="S2" s="63"/>
-      <c r="T2" s="63"/>
-      <c r="U2" s="63"/>
-      <c r="V2" s="63"/>
-      <c r="W2" s="63"/>
-      <c r="X2" s="63"/>
-      <c r="Y2" s="63"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="41"/>
+      <c r="R2" s="41"/>
+      <c r="S2" s="41"/>
+      <c r="T2" s="41"/>
+      <c r="U2" s="41"/>
+      <c r="V2" s="41"/>
+      <c r="W2" s="41"/>
+      <c r="X2" s="41"/>
+      <c r="Y2" s="41"/>
       <c r="Z2" s="22"/>
       <c r="AC2" s="24"/>
       <c r="AD2" s="2" t="s">
@@ -1849,24 +1845,24 @@
     </row>
     <row r="3" spans="1:34" ht="5.0999999999999996" customHeight="1"/>
     <row r="4" spans="1:34" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="77" t="s">
+      <c r="A4" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="78"/>
-      <c r="L4" s="77" t="s">
+      <c r="B4" s="33"/>
+      <c r="L4" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="M4" s="78"/>
+      <c r="M4" s="33"/>
       <c r="N4" s="9"/>
-      <c r="X4" s="35" t="s">
+      <c r="X4" s="71" t="s">
         <v>109</v>
       </c>
-      <c r="Y4" s="35"/>
+      <c r="Y4" s="71"/>
       <c r="Z4" s="3"/>
-      <c r="AD4" s="66" t="s">
+      <c r="AD4" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="AE4" s="66"/>
+      <c r="AE4" s="44"/>
       <c r="AF4" s="4"/>
       <c r="AG4" s="5" t="s">
         <v>5</v>
@@ -1879,39 +1875,39 @@
       <c r="A5" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="44" t="s">
+      <c r="B5" s="77" t="s">
         <v>112</v>
       </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="46"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="79"/>
       <c r="F5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="47" t="s">
+      <c r="G5" s="80" t="s">
         <v>113</v>
       </c>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="46"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="79"/>
       <c r="L5" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="M5" s="51" t="s">
+      <c r="M5" s="55" t="s">
         <v>119</v>
       </c>
-      <c r="N5" s="51"/>
-      <c r="O5" s="52"/>
-      <c r="P5" s="52"/>
-      <c r="Q5" s="52"/>
-      <c r="R5" s="52"/>
-      <c r="S5" s="52"/>
-      <c r="T5" s="52"/>
-      <c r="U5" s="52"/>
-      <c r="V5" s="52"/>
-      <c r="W5" s="52"/>
-      <c r="X5" s="52"/>
-      <c r="Y5" s="53"/>
+      <c r="N5" s="55"/>
+      <c r="O5" s="56"/>
+      <c r="P5" s="56"/>
+      <c r="Q5" s="56"/>
+      <c r="R5" s="56"/>
+      <c r="S5" s="56"/>
+      <c r="T5" s="56"/>
+      <c r="U5" s="56"/>
+      <c r="V5" s="56"/>
+      <c r="W5" s="56"/>
+      <c r="X5" s="56"/>
+      <c r="Y5" s="57"/>
       <c r="Z5" s="25"/>
       <c r="AD5" t="s">
         <v>63</v>
@@ -1928,19 +1924,19 @@
       <c r="A6" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="51" t="s">
         <v>114</v>
       </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="34"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="52"/>
       <c r="F6" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="64" t="s">
+      <c r="G6" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="H6" s="65"/>
+      <c r="H6" s="43"/>
       <c r="I6" s="13" t="s">
         <v>99</v>
       </c>
@@ -1950,23 +1946,23 @@
       <c r="L6" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M6" s="32"/>
-      <c r="N6" s="33"/>
-      <c r="O6" s="33"/>
-      <c r="P6" s="33"/>
-      <c r="Q6" s="34"/>
-      <c r="R6" s="36" t="s">
+      <c r="M6" s="70"/>
+      <c r="N6" s="51"/>
+      <c r="O6" s="51"/>
+      <c r="P6" s="51"/>
+      <c r="Q6" s="52"/>
+      <c r="R6" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="S6" s="36"/>
-      <c r="T6" s="43" t="s">
+      <c r="S6" s="72"/>
+      <c r="T6" s="76" t="s">
         <v>120</v>
       </c>
-      <c r="U6" s="43"/>
-      <c r="V6" s="43"/>
-      <c r="W6" s="43"/>
-      <c r="X6" s="43"/>
-      <c r="Y6" s="43"/>
+      <c r="U6" s="76"/>
+      <c r="V6" s="76"/>
+      <c r="W6" s="76"/>
+      <c r="X6" s="76"/>
+      <c r="Y6" s="76"/>
       <c r="Z6" s="26"/>
       <c r="AA6" s="2" t="str">
         <f>IF(VALUE(B6)&gt;0,TEXT(VALUE(B6)+19110000,"@"),"")</f>
@@ -1995,39 +1991,39 @@
       <c r="A7" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="51" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="34"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="52"/>
       <c r="F7" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="48" t="s">
+      <c r="G7" s="81" t="s">
         <v>117</v>
       </c>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="50"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="82"/>
+      <c r="J7" s="83"/>
       <c r="L7" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="M7" s="51" t="s">
+      <c r="M7" s="55" t="s">
         <v>121</v>
       </c>
-      <c r="N7" s="51"/>
-      <c r="O7" s="52"/>
-      <c r="P7" s="52"/>
-      <c r="Q7" s="52"/>
-      <c r="R7" s="52"/>
-      <c r="S7" s="52"/>
-      <c r="T7" s="52"/>
-      <c r="U7" s="52"/>
-      <c r="V7" s="52"/>
-      <c r="W7" s="52"/>
-      <c r="X7" s="52"/>
-      <c r="Y7" s="53"/>
+      <c r="N7" s="55"/>
+      <c r="O7" s="56"/>
+      <c r="P7" s="56"/>
+      <c r="Q7" s="56"/>
+      <c r="R7" s="56"/>
+      <c r="S7" s="56"/>
+      <c r="T7" s="56"/>
+      <c r="U7" s="56"/>
+      <c r="V7" s="56"/>
+      <c r="W7" s="56"/>
+      <c r="X7" s="56"/>
+      <c r="Y7" s="57"/>
       <c r="Z7" s="25"/>
       <c r="AA7" s="2" t="str">
         <f>IF(VALUE(B7)&gt;0,TEXT(VALUE(B7)+19110000,"@"),"")</f>
@@ -2056,17 +2052,17 @@
       <c r="A8" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="34"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="52"/>
       <c r="F8" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="34"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="52"/>
       <c r="L8" s="16" t="s">
         <v>24</v>
       </c>
@@ -2076,21 +2072,21 @@
       <c r="N8" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="O8" s="37">
+      <c r="O8" s="73">
         <v>4</v>
       </c>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="38" t="s">
+      <c r="P8" s="73"/>
+      <c r="Q8" s="74" t="s">
         <v>98</v>
       </c>
-      <c r="R8" s="38"/>
-      <c r="S8" s="38"/>
-      <c r="T8" s="38"/>
-      <c r="U8" s="38"/>
-      <c r="V8" s="38"/>
-      <c r="W8" s="38"/>
-      <c r="X8" s="38"/>
-      <c r="Y8" s="39"/>
+      <c r="R8" s="74"/>
+      <c r="S8" s="74"/>
+      <c r="T8" s="74"/>
+      <c r="U8" s="74"/>
+      <c r="V8" s="74"/>
+      <c r="W8" s="74"/>
+      <c r="X8" s="74"/>
+      <c r="Y8" s="75"/>
       <c r="Z8" s="29"/>
       <c r="AD8" t="s">
         <v>65</v>
@@ -2107,68 +2103,68 @@
       <c r="A9" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="72" t="s">
+      <c r="B9" s="58" t="s">
         <v>118</v>
       </c>
-      <c r="C9" s="73"/>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73"/>
-      <c r="G9" s="73"/>
-      <c r="H9" s="73"/>
-      <c r="I9" s="73"/>
-      <c r="J9" s="74"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="60"/>
       <c r="L9" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="M9" s="40">
+      <c r="M9" s="48">
         <v>100000</v>
       </c>
-      <c r="N9" s="40"/>
-      <c r="O9" s="41"/>
-      <c r="P9" s="41"/>
-      <c r="Q9" s="41"/>
-      <c r="R9" s="41"/>
-      <c r="S9" s="41"/>
-      <c r="T9" s="41"/>
-      <c r="U9" s="41"/>
-      <c r="V9" s="41"/>
-      <c r="W9" s="41"/>
-      <c r="X9" s="41"/>
-      <c r="Y9" s="42"/>
+      <c r="N9" s="48"/>
+      <c r="O9" s="49"/>
+      <c r="P9" s="49"/>
+      <c r="Q9" s="49"/>
+      <c r="R9" s="49"/>
+      <c r="S9" s="49"/>
+      <c r="T9" s="49"/>
+      <c r="U9" s="49"/>
+      <c r="V9" s="49"/>
+      <c r="W9" s="49"/>
+      <c r="X9" s="49"/>
+      <c r="Y9" s="50"/>
       <c r="Z9" s="27"/>
     </row>
     <row r="10" spans="1:34" ht="39.950000000000003" customHeight="1">
       <c r="A10" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="70" t="s">
+      <c r="B10" s="53" t="s">
         <v>110</v>
       </c>
-      <c r="C10" s="70"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="70"/>
-      <c r="J10" s="71"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="54"/>
       <c r="L10" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="M10" s="40"/>
-      <c r="N10" s="40"/>
-      <c r="O10" s="41"/>
-      <c r="P10" s="41"/>
-      <c r="Q10" s="41"/>
-      <c r="R10" s="41"/>
-      <c r="S10" s="41"/>
-      <c r="T10" s="41"/>
-      <c r="U10" s="41"/>
-      <c r="V10" s="41"/>
-      <c r="W10" s="41"/>
-      <c r="X10" s="41"/>
-      <c r="Y10" s="42"/>
+      <c r="M10" s="48"/>
+      <c r="N10" s="48"/>
+      <c r="O10" s="49"/>
+      <c r="P10" s="49"/>
+      <c r="Q10" s="49"/>
+      <c r="R10" s="49"/>
+      <c r="S10" s="49"/>
+      <c r="T10" s="49"/>
+      <c r="U10" s="49"/>
+      <c r="V10" s="49"/>
+      <c r="W10" s="49"/>
+      <c r="X10" s="49"/>
+      <c r="Y10" s="50"/>
       <c r="Z10" s="27"/>
     </row>
     <row r="11" spans="1:34" ht="5.0999999999999996" customHeight="1">
@@ -2183,71 +2179,71 @@
       <c r="J11" s="3"/>
     </row>
     <row r="12" spans="1:34" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="77" t="s">
+      <c r="A12" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="78"/>
-      <c r="L12" s="77" t="s">
+      <c r="B12" s="33"/>
+      <c r="L12" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="M12" s="78"/>
+      <c r="M12" s="33"/>
       <c r="N12" s="9"/>
-      <c r="O12" s="69"/>
-      <c r="P12" s="69"/>
-      <c r="Q12" s="69"/>
-      <c r="R12" s="69"/>
-      <c r="S12" s="69"/>
-      <c r="T12" s="69"/>
-      <c r="U12" s="69"/>
-      <c r="V12" s="69"/>
-      <c r="W12" s="69"/>
-      <c r="X12" s="69"/>
-      <c r="Y12" s="69"/>
+      <c r="O12" s="47"/>
+      <c r="P12" s="47"/>
+      <c r="Q12" s="47"/>
+      <c r="R12" s="47"/>
+      <c r="S12" s="47"/>
+      <c r="T12" s="47"/>
+      <c r="U12" s="47"/>
+      <c r="V12" s="47"/>
+      <c r="W12" s="47"/>
+      <c r="X12" s="47"/>
+      <c r="Y12" s="47"/>
       <c r="Z12" s="23"/>
     </row>
     <row r="13" spans="1:34" ht="39.950000000000003" customHeight="1">
       <c r="A13" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="67">
+      <c r="B13" s="45">
         <v>300000</v>
       </c>
-      <c r="C13" s="67"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
       <c r="F13" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G13" s="68">
+      <c r="G13" s="46">
         <v>24</v>
       </c>
-      <c r="H13" s="68"/>
-      <c r="I13" s="68"/>
-      <c r="J13" s="65"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
+      <c r="J13" s="43"/>
       <c r="L13" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M13" s="79" t="s">
+      <c r="M13" s="34" t="s">
         <v>122</v>
       </c>
-      <c r="N13" s="80"/>
-      <c r="O13" s="81"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="36"/>
       <c r="P13" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="Q13" s="56" t="s">
+      <c r="Q13" s="62" t="s">
         <v>124</v>
       </c>
-      <c r="R13" s="57"/>
+      <c r="R13" s="63"/>
       <c r="S13" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="T13" s="59" t="s">
+      <c r="T13" s="65" t="s">
         <v>125</v>
       </c>
-      <c r="U13" s="60"/>
-      <c r="V13" s="60"/>
-      <c r="W13" s="60"/>
+      <c r="U13" s="66"/>
+      <c r="V13" s="66"/>
+      <c r="W13" s="66"/>
       <c r="X13" s="13" t="s">
         <v>95</v>
       </c>
@@ -2258,47 +2254,47 @@
       <c r="A14" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="75">
+      <c r="B14" s="30">
         <f>IF(ISERROR($AE$8),"",$AE$8)</f>
         <v>14653</v>
       </c>
-      <c r="C14" s="75"/>
-      <c r="D14" s="75"/>
-      <c r="E14" s="75"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
       <c r="F14" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="75">
+      <c r="G14" s="30">
         <f xml:space="preserve"> IF(ISERROR($G$13*$B$14),"",$G$13*$B$14)</f>
         <v>351672</v>
       </c>
-      <c r="H14" s="75"/>
-      <c r="I14" s="75"/>
-      <c r="J14" s="76"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="31"/>
       <c r="L14" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="M14" s="82" t="s">
+      <c r="M14" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="N14" s="83"/>
-      <c r="O14" s="84"/>
+      <c r="N14" s="38"/>
+      <c r="O14" s="39"/>
       <c r="P14" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="Q14" s="56" t="s">
+      <c r="Q14" s="62" t="s">
         <v>111</v>
       </c>
-      <c r="R14" s="57"/>
+      <c r="R14" s="63"/>
       <c r="S14" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="T14" s="59" t="s">
+      <c r="T14" s="65" t="s">
         <v>126</v>
       </c>
-      <c r="U14" s="60"/>
-      <c r="V14" s="60"/>
-      <c r="W14" s="60"/>
+      <c r="U14" s="66"/>
+      <c r="V14" s="66"/>
+      <c r="W14" s="66"/>
       <c r="X14" s="13" t="s">
         <v>95</v>
       </c>
@@ -2306,36 +2302,36 @@
       <c r="Z14" s="28"/>
     </row>
     <row r="15" spans="1:34" ht="39.950000000000003" customHeight="1">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="68" t="s">
         <v>108</v>
       </c>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
+      <c r="B15" s="68"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="68"/>
+      <c r="G15" s="68"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="68"/>
+      <c r="J15" s="68"/>
       <c r="L15" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="M15" s="55"/>
-      <c r="N15" s="55"/>
-      <c r="O15" s="55"/>
+      <c r="M15" s="61"/>
+      <c r="N15" s="61"/>
+      <c r="O15" s="61"/>
       <c r="P15" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="Q15" s="58"/>
-      <c r="R15" s="58"/>
+      <c r="Q15" s="64"/>
+      <c r="R15" s="64"/>
       <c r="S15" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="T15" s="61"/>
-      <c r="U15" s="61"/>
-      <c r="V15" s="61"/>
-      <c r="W15" s="61"/>
+      <c r="T15" s="67"/>
+      <c r="U15" s="67"/>
+      <c r="V15" s="67"/>
+      <c r="W15" s="67"/>
       <c r="X15" s="13" t="s">
         <v>95</v>
       </c>
@@ -2343,30 +2339,30 @@
       <c r="Z15" s="28"/>
     </row>
     <row r="16" spans="1:34">
-      <c r="A16" s="31"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
-      <c r="L16" s="54"/>
-      <c r="M16" s="54"/>
+      <c r="A16" s="69"/>
+      <c r="B16" s="69"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="69"/>
+      <c r="H16" s="69"/>
+      <c r="I16" s="69"/>
+      <c r="J16" s="69"/>
+      <c r="L16" s="84"/>
+      <c r="M16" s="84"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-      <c r="Q16" s="54"/>
-      <c r="R16" s="54"/>
-      <c r="S16" s="54"/>
+      <c r="Q16" s="84"/>
+      <c r="R16" s="84"/>
+      <c r="S16" s="84"/>
       <c r="T16" s="3"/>
-      <c r="U16" s="54"/>
-      <c r="V16" s="54"/>
-      <c r="W16" s="54"/>
-      <c r="X16" s="54"/>
-      <c r="Y16" s="54"/>
+      <c r="U16" s="84"/>
+      <c r="V16" s="84"/>
+      <c r="W16" s="84"/>
+      <c r="X16" s="84"/>
+      <c r="Y16" s="84"/>
       <c r="Z16" s="3"/>
     </row>
     <row r="17" s="2" customFormat="1"/>
@@ -2378,35 +2374,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="pSlU5FB8qUpeOzKaozvtSIzWW8yLrAQ53qJovs9ylgNLN8Gz4hPNC4BY3SbvnE63VuL6ZUYn55WAl7B8Jgt6cQ==" saltValue="HuraIeCnbixDfus1I0foHQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="45">
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="M13:O13"/>
-    <mergeCell ref="M14:O14"/>
-    <mergeCell ref="A1:Y1"/>
-    <mergeCell ref="A2:Y2"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="AD4:AE4"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="G13:J13"/>
-    <mergeCell ref="O12:Y12"/>
-    <mergeCell ref="M10:Y10"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="B10:J10"/>
-    <mergeCell ref="M7:Y7"/>
-    <mergeCell ref="B9:J9"/>
-    <mergeCell ref="M15:O15"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="T13:W13"/>
-    <mergeCell ref="T14:W14"/>
-    <mergeCell ref="T15:W15"/>
     <mergeCell ref="A15:J16"/>
     <mergeCell ref="M6:Q6"/>
     <mergeCell ref="X4:Y4"/>
@@ -2423,6 +2390,35 @@
     <mergeCell ref="L16:M16"/>
     <mergeCell ref="Q16:S16"/>
     <mergeCell ref="U16:Y16"/>
+    <mergeCell ref="M15:O15"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="Q14:R14"/>
+    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="T13:W13"/>
+    <mergeCell ref="T14:W14"/>
+    <mergeCell ref="T15:W15"/>
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A2:Y2"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="AD4:AE4"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="G13:J13"/>
+    <mergeCell ref="O12:Y12"/>
+    <mergeCell ref="M10:Y10"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="B10:J10"/>
+    <mergeCell ref="M7:Y7"/>
+    <mergeCell ref="B9:J9"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="M14:O14"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A5">

--- a/申請書/第一申請書範本.xlsx
+++ b/申請書/第一申請書範本.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fbf32e69ea87f61e/Desktop/claude/申請書/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="623" documentId="8_{8657E013-8DDC-4972-BDBF-6C2620C0497F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42FD3C7F-7D1A-4DDF-BDCA-57E302D7C2A1}"/>
+  <xr:revisionPtr revIDLastSave="628" documentId="8_{8657E013-8DDC-4972-BDBF-6C2620C0497F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1C6AD8E-4B43-43C2-AC48-B1514BFF4D6A}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="BwhljbYaKav+E17RuyDNCkx7FNkCIijIIhGeSyh/zEvLWC29IGnQmrBFwgnc+icxQOJkDEe40IlAn/u+KarW+w==" workbookSaltValue="AzwUdSEg380nYmyDCj3oGQ==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-1605" yWindow="945" windowWidth="17340" windowHeight="13485" xr2:uid="{1319B317-115B-4189-827F-8B258237D3A2}"/>
+    <workbookView xWindow="12960" yWindow="2805" windowWidth="23595" windowHeight="13485" xr2:uid="{1319B317-115B-4189-827F-8B258237D3A2}"/>
   </bookViews>
   <sheets>
     <sheet name="申請書" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="129">
   <si>
     <t>基本資料</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -530,6 +530,12 @@
   <si>
     <t>0975130357</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>　</t>
   </si>
 </sst>
 </file>
@@ -1052,39 +1058,124 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1116,26 +1207,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -1144,18 +1215,6 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -1168,94 +1227,41 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="177" fontId="5" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1463,6 +1469,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1777,63 +1787,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="25.5" customHeight="1">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="40"/>
-      <c r="P1" s="40"/>
-      <c r="Q1" s="40"/>
-      <c r="R1" s="40"/>
-      <c r="S1" s="40"/>
-      <c r="T1" s="40"/>
-      <c r="U1" s="40"/>
-      <c r="V1" s="40"/>
-      <c r="W1" s="40"/>
-      <c r="X1" s="40"/>
-      <c r="Y1" s="40"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
+      <c r="S1" s="62"/>
+      <c r="T1" s="62"/>
+      <c r="U1" s="62"/>
+      <c r="V1" s="62"/>
+      <c r="W1" s="62"/>
+      <c r="X1" s="62"/>
+      <c r="Y1" s="62"/>
       <c r="Z1" s="21"/>
     </row>
     <row r="2" spans="1:34" ht="25.5" customHeight="1">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="63" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="41"/>
-      <c r="S2" s="41"/>
-      <c r="T2" s="41"/>
-      <c r="U2" s="41"/>
-      <c r="V2" s="41"/>
-      <c r="W2" s="41"/>
-      <c r="X2" s="41"/>
-      <c r="Y2" s="41"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="63"/>
+      <c r="V2" s="63"/>
+      <c r="W2" s="63"/>
+      <c r="X2" s="63"/>
+      <c r="Y2" s="63"/>
       <c r="Z2" s="22"/>
       <c r="AC2" s="24"/>
       <c r="AD2" s="2" t="s">
@@ -1845,24 +1855,24 @@
     </row>
     <row r="3" spans="1:34" ht="5.0999999999999996" customHeight="1"/>
     <row r="4" spans="1:34" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="L4" s="32" t="s">
+      <c r="B4" s="78"/>
+      <c r="L4" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="M4" s="33"/>
+      <c r="M4" s="78"/>
       <c r="N4" s="9"/>
-      <c r="X4" s="71" t="s">
+      <c r="X4" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="Y4" s="71"/>
+      <c r="Y4" s="35"/>
       <c r="Z4" s="3"/>
-      <c r="AD4" s="44" t="s">
+      <c r="AD4" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="AE4" s="44"/>
+      <c r="AE4" s="66"/>
       <c r="AF4" s="4"/>
       <c r="AG4" s="5" t="s">
         <v>5</v>
@@ -1875,39 +1885,39 @@
       <c r="A5" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="44" t="s">
         <v>112</v>
       </c>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="79"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="46"/>
       <c r="F5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="80" t="s">
+      <c r="G5" s="47" t="s">
         <v>113</v>
       </c>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="79"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="46"/>
       <c r="L5" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="M5" s="55" t="s">
+      <c r="M5" s="51" t="s">
         <v>119</v>
       </c>
-      <c r="N5" s="55"/>
-      <c r="O5" s="56"/>
-      <c r="P5" s="56"/>
-      <c r="Q5" s="56"/>
-      <c r="R5" s="56"/>
-      <c r="S5" s="56"/>
-      <c r="T5" s="56"/>
-      <c r="U5" s="56"/>
-      <c r="V5" s="56"/>
-      <c r="W5" s="56"/>
-      <c r="X5" s="56"/>
-      <c r="Y5" s="57"/>
+      <c r="N5" s="51"/>
+      <c r="O5" s="52"/>
+      <c r="P5" s="52"/>
+      <c r="Q5" s="52"/>
+      <c r="R5" s="52"/>
+      <c r="S5" s="52"/>
+      <c r="T5" s="52"/>
+      <c r="U5" s="52"/>
+      <c r="V5" s="52"/>
+      <c r="W5" s="52"/>
+      <c r="X5" s="52"/>
+      <c r="Y5" s="53"/>
       <c r="Z5" s="25"/>
       <c r="AD5" t="s">
         <v>63</v>
@@ -1924,19 +1934,19 @@
       <c r="A6" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="51" t="s">
+      <c r="B6" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="52"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="34"/>
       <c r="F6" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="42" t="s">
+      <c r="G6" s="64" t="s">
         <v>68</v>
       </c>
-      <c r="H6" s="43"/>
+      <c r="H6" s="65"/>
       <c r="I6" s="13" t="s">
         <v>99</v>
       </c>
@@ -1946,23 +1956,23 @@
       <c r="L6" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M6" s="70"/>
-      <c r="N6" s="51"/>
-      <c r="O6" s="51"/>
-      <c r="P6" s="51"/>
-      <c r="Q6" s="52"/>
-      <c r="R6" s="72" t="s">
+      <c r="M6" s="32"/>
+      <c r="N6" s="33"/>
+      <c r="O6" s="33"/>
+      <c r="P6" s="33"/>
+      <c r="Q6" s="34"/>
+      <c r="R6" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="S6" s="72"/>
-      <c r="T6" s="76" t="s">
+      <c r="S6" s="36"/>
+      <c r="T6" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="U6" s="76"/>
-      <c r="V6" s="76"/>
-      <c r="W6" s="76"/>
-      <c r="X6" s="76"/>
-      <c r="Y6" s="76"/>
+      <c r="U6" s="43"/>
+      <c r="V6" s="43"/>
+      <c r="W6" s="43"/>
+      <c r="X6" s="43"/>
+      <c r="Y6" s="43"/>
       <c r="Z6" s="26"/>
       <c r="AA6" s="2" t="str">
         <f>IF(VALUE(B6)&gt;0,TEXT(VALUE(B6)+19110000,"@"),"")</f>
@@ -1991,39 +2001,39 @@
       <c r="A7" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="52"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="34"/>
       <c r="F7" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="81" t="s">
+      <c r="G7" s="48" t="s">
         <v>117</v>
       </c>
-      <c r="H7" s="82"/>
-      <c r="I7" s="82"/>
-      <c r="J7" s="83"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="50"/>
       <c r="L7" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="M7" s="55" t="s">
+      <c r="M7" s="51" t="s">
         <v>121</v>
       </c>
-      <c r="N7" s="55"/>
-      <c r="O7" s="56"/>
-      <c r="P7" s="56"/>
-      <c r="Q7" s="56"/>
-      <c r="R7" s="56"/>
-      <c r="S7" s="56"/>
-      <c r="T7" s="56"/>
-      <c r="U7" s="56"/>
-      <c r="V7" s="56"/>
-      <c r="W7" s="56"/>
-      <c r="X7" s="56"/>
-      <c r="Y7" s="57"/>
+      <c r="N7" s="51"/>
+      <c r="O7" s="52"/>
+      <c r="P7" s="52"/>
+      <c r="Q7" s="52"/>
+      <c r="R7" s="52"/>
+      <c r="S7" s="52"/>
+      <c r="T7" s="52"/>
+      <c r="U7" s="52"/>
+      <c r="V7" s="52"/>
+      <c r="W7" s="52"/>
+      <c r="X7" s="52"/>
+      <c r="Y7" s="53"/>
       <c r="Z7" s="25"/>
       <c r="AA7" s="2" t="str">
         <f>IF(VALUE(B7)&gt;0,TEXT(VALUE(B7)+19110000,"@"),"")</f>
@@ -2052,17 +2062,17 @@
       <c r="A8" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="52"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="34"/>
       <c r="F8" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="52"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="34"/>
       <c r="L8" s="16" t="s">
         <v>24</v>
       </c>
@@ -2072,21 +2082,21 @@
       <c r="N8" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="O8" s="73">
+      <c r="O8" s="37">
         <v>4</v>
       </c>
-      <c r="P8" s="73"/>
-      <c r="Q8" s="74" t="s">
+      <c r="P8" s="37"/>
+      <c r="Q8" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="R8" s="74"/>
-      <c r="S8" s="74"/>
-      <c r="T8" s="74"/>
-      <c r="U8" s="74"/>
-      <c r="V8" s="74"/>
-      <c r="W8" s="74"/>
-      <c r="X8" s="74"/>
-      <c r="Y8" s="75"/>
+      <c r="R8" s="38"/>
+      <c r="S8" s="38"/>
+      <c r="T8" s="38"/>
+      <c r="U8" s="38"/>
+      <c r="V8" s="38"/>
+      <c r="W8" s="38"/>
+      <c r="X8" s="38"/>
+      <c r="Y8" s="39"/>
       <c r="Z8" s="29"/>
       <c r="AD8" t="s">
         <v>65</v>
@@ -2103,68 +2113,68 @@
       <c r="A9" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="58" t="s">
+      <c r="B9" s="72" t="s">
         <v>118</v>
       </c>
-      <c r="C9" s="59"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="59"/>
-      <c r="J9" s="60"/>
+      <c r="C9" s="73"/>
+      <c r="D9" s="73"/>
+      <c r="E9" s="73"/>
+      <c r="F9" s="73"/>
+      <c r="G9" s="73"/>
+      <c r="H9" s="73"/>
+      <c r="I9" s="73"/>
+      <c r="J9" s="74"/>
       <c r="L9" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="M9" s="48">
+      <c r="M9" s="40">
         <v>100000</v>
       </c>
-      <c r="N9" s="48"/>
-      <c r="O9" s="49"/>
-      <c r="P9" s="49"/>
-      <c r="Q9" s="49"/>
-      <c r="R9" s="49"/>
-      <c r="S9" s="49"/>
-      <c r="T9" s="49"/>
-      <c r="U9" s="49"/>
-      <c r="V9" s="49"/>
-      <c r="W9" s="49"/>
-      <c r="X9" s="49"/>
-      <c r="Y9" s="50"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="41"/>
+      <c r="P9" s="41"/>
+      <c r="Q9" s="41"/>
+      <c r="R9" s="41"/>
+      <c r="S9" s="41"/>
+      <c r="T9" s="41"/>
+      <c r="U9" s="41"/>
+      <c r="V9" s="41"/>
+      <c r="W9" s="41"/>
+      <c r="X9" s="41"/>
+      <c r="Y9" s="42"/>
       <c r="Z9" s="27"/>
     </row>
     <row r="10" spans="1:34" ht="39.950000000000003" customHeight="1">
       <c r="A10" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="53" t="s">
+      <c r="B10" s="70" t="s">
         <v>110</v>
       </c>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="54"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="70"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="71"/>
       <c r="L10" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="M10" s="48"/>
-      <c r="N10" s="48"/>
-      <c r="O10" s="49"/>
-      <c r="P10" s="49"/>
-      <c r="Q10" s="49"/>
-      <c r="R10" s="49"/>
-      <c r="S10" s="49"/>
-      <c r="T10" s="49"/>
-      <c r="U10" s="49"/>
-      <c r="V10" s="49"/>
-      <c r="W10" s="49"/>
-      <c r="X10" s="49"/>
-      <c r="Y10" s="50"/>
+      <c r="M10" s="40"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="41"/>
+      <c r="P10" s="41"/>
+      <c r="Q10" s="41"/>
+      <c r="R10" s="41"/>
+      <c r="S10" s="41"/>
+      <c r="T10" s="41"/>
+      <c r="U10" s="41"/>
+      <c r="V10" s="41"/>
+      <c r="W10" s="41"/>
+      <c r="X10" s="41"/>
+      <c r="Y10" s="42"/>
       <c r="Z10" s="27"/>
     </row>
     <row r="11" spans="1:34" ht="5.0999999999999996" customHeight="1">
@@ -2179,159 +2189,163 @@
       <c r="J11" s="3"/>
     </row>
     <row r="12" spans="1:34" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="32" t="s">
+      <c r="A12" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="33"/>
-      <c r="L12" s="32" t="s">
+      <c r="B12" s="78"/>
+      <c r="L12" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="M12" s="33"/>
+      <c r="M12" s="78"/>
       <c r="N12" s="9"/>
-      <c r="O12" s="47"/>
-      <c r="P12" s="47"/>
-      <c r="Q12" s="47"/>
-      <c r="R12" s="47"/>
-      <c r="S12" s="47"/>
-      <c r="T12" s="47"/>
-      <c r="U12" s="47"/>
-      <c r="V12" s="47"/>
-      <c r="W12" s="47"/>
-      <c r="X12" s="47"/>
-      <c r="Y12" s="47"/>
+      <c r="O12" s="69"/>
+      <c r="P12" s="69"/>
+      <c r="Q12" s="69"/>
+      <c r="R12" s="69"/>
+      <c r="S12" s="69"/>
+      <c r="T12" s="69"/>
+      <c r="U12" s="69"/>
+      <c r="V12" s="69"/>
+      <c r="W12" s="69"/>
+      <c r="X12" s="69"/>
+      <c r="Y12" s="69"/>
       <c r="Z12" s="23"/>
     </row>
     <row r="13" spans="1:34" ht="39.950000000000003" customHeight="1">
       <c r="A13" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="45">
+      <c r="B13" s="67">
         <v>300000</v>
       </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
       <c r="F13" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G13" s="46">
+      <c r="G13" s="68">
         <v>24</v>
       </c>
-      <c r="H13" s="46"/>
-      <c r="I13" s="46"/>
-      <c r="J13" s="43"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="68"/>
+      <c r="J13" s="65"/>
       <c r="L13" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M13" s="34" t="s">
+      <c r="M13" s="79" t="s">
         <v>122</v>
       </c>
-      <c r="N13" s="35"/>
-      <c r="O13" s="36"/>
+      <c r="N13" s="80"/>
+      <c r="O13" s="81"/>
       <c r="P13" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="Q13" s="62" t="s">
+      <c r="Q13" s="56" t="s">
         <v>124</v>
       </c>
-      <c r="R13" s="63"/>
+      <c r="R13" s="57"/>
       <c r="S13" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="T13" s="65" t="s">
+      <c r="T13" s="59" t="s">
         <v>125</v>
       </c>
-      <c r="U13" s="66"/>
-      <c r="V13" s="66"/>
-      <c r="W13" s="66"/>
+      <c r="U13" s="60"/>
+      <c r="V13" s="60"/>
+      <c r="W13" s="60"/>
       <c r="X13" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="Y13" s="11"/>
+      <c r="Y13" s="11" t="s">
+        <v>128</v>
+      </c>
       <c r="Z13" s="28"/>
     </row>
     <row r="14" spans="1:34" ht="39.950000000000003" customHeight="1">
       <c r="A14" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="75">
         <f>IF(ISERROR($AE$8),"",$AE$8)</f>
         <v>14653</v>
       </c>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="75"/>
+      <c r="E14" s="75"/>
       <c r="F14" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="75">
         <f xml:space="preserve"> IF(ISERROR($G$13*$B$14),"",$G$13*$B$14)</f>
         <v>351672</v>
       </c>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="31"/>
+      <c r="H14" s="75"/>
+      <c r="I14" s="75"/>
+      <c r="J14" s="76"/>
       <c r="L14" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="M14" s="37" t="s">
+      <c r="M14" s="82" t="s">
         <v>123</v>
       </c>
-      <c r="N14" s="38"/>
-      <c r="O14" s="39"/>
+      <c r="N14" s="83"/>
+      <c r="O14" s="84"/>
       <c r="P14" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="Q14" s="62" t="s">
+      <c r="Q14" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="R14" s="63"/>
+      <c r="R14" s="57"/>
       <c r="S14" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="T14" s="65" t="s">
+      <c r="T14" s="59" t="s">
         <v>126</v>
       </c>
-      <c r="U14" s="66"/>
-      <c r="V14" s="66"/>
-      <c r="W14" s="66"/>
+      <c r="U14" s="60"/>
+      <c r="V14" s="60"/>
+      <c r="W14" s="60"/>
       <c r="X14" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="Y14" s="11"/>
+      <c r="Y14" s="11" t="s">
+        <v>127</v>
+      </c>
       <c r="Z14" s="28"/>
     </row>
     <row r="15" spans="1:34" ht="39.950000000000003" customHeight="1">
-      <c r="A15" s="68" t="s">
+      <c r="A15" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="B15" s="68"/>
-      <c r="C15" s="68"/>
-      <c r="D15" s="68"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="68"/>
-      <c r="G15" s="68"/>
-      <c r="H15" s="68"/>
-      <c r="I15" s="68"/>
-      <c r="J15" s="68"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
       <c r="L15" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="M15" s="61"/>
-      <c r="N15" s="61"/>
-      <c r="O15" s="61"/>
+      <c r="M15" s="55"/>
+      <c r="N15" s="55"/>
+      <c r="O15" s="55"/>
       <c r="P15" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="Q15" s="64"/>
-      <c r="R15" s="64"/>
+      <c r="Q15" s="58"/>
+      <c r="R15" s="58"/>
       <c r="S15" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="T15" s="67"/>
-      <c r="U15" s="67"/>
-      <c r="V15" s="67"/>
-      <c r="W15" s="67"/>
+      <c r="T15" s="61"/>
+      <c r="U15" s="61"/>
+      <c r="V15" s="61"/>
+      <c r="W15" s="61"/>
       <c r="X15" s="13" t="s">
         <v>95</v>
       </c>
@@ -2339,30 +2353,30 @@
       <c r="Z15" s="28"/>
     </row>
     <row r="16" spans="1:34">
-      <c r="A16" s="69"/>
-      <c r="B16" s="69"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="69"/>
-      <c r="I16" s="69"/>
-      <c r="J16" s="69"/>
-      <c r="L16" s="84"/>
-      <c r="M16" s="84"/>
+      <c r="A16" s="31"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="L16" s="54"/>
+      <c r="M16" s="54"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-      <c r="Q16" s="84"/>
-      <c r="R16" s="84"/>
-      <c r="S16" s="84"/>
+      <c r="Q16" s="54"/>
+      <c r="R16" s="54"/>
+      <c r="S16" s="54"/>
       <c r="T16" s="3"/>
-      <c r="U16" s="84"/>
-      <c r="V16" s="84"/>
-      <c r="W16" s="84"/>
-      <c r="X16" s="84"/>
-      <c r="Y16" s="84"/>
+      <c r="U16" s="54"/>
+      <c r="V16" s="54"/>
+      <c r="W16" s="54"/>
+      <c r="X16" s="54"/>
+      <c r="Y16" s="54"/>
       <c r="Z16" s="3"/>
     </row>
     <row r="17" s="2" customFormat="1"/>
@@ -2374,6 +2388,35 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="pSlU5FB8qUpeOzKaozvtSIzWW8yLrAQ53qJovs9ylgNLN8Gz4hPNC4BY3SbvnE63VuL6ZUYn55WAl7B8Jgt6cQ==" saltValue="HuraIeCnbixDfus1I0foHQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="45">
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="M14:O14"/>
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A2:Y2"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="AD4:AE4"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="G13:J13"/>
+    <mergeCell ref="O12:Y12"/>
+    <mergeCell ref="M10:Y10"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="B10:J10"/>
+    <mergeCell ref="M7:Y7"/>
+    <mergeCell ref="B9:J9"/>
+    <mergeCell ref="M15:O15"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="Q14:R14"/>
+    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="T13:W13"/>
+    <mergeCell ref="T14:W14"/>
+    <mergeCell ref="T15:W15"/>
     <mergeCell ref="A15:J16"/>
     <mergeCell ref="M6:Q6"/>
     <mergeCell ref="X4:Y4"/>
@@ -2390,35 +2433,6 @@
     <mergeCell ref="L16:M16"/>
     <mergeCell ref="Q16:S16"/>
     <mergeCell ref="U16:Y16"/>
-    <mergeCell ref="M15:O15"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="T13:W13"/>
-    <mergeCell ref="T14:W14"/>
-    <mergeCell ref="T15:W15"/>
-    <mergeCell ref="A1:Y1"/>
-    <mergeCell ref="A2:Y2"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="AD4:AE4"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="G13:J13"/>
-    <mergeCell ref="O12:Y12"/>
-    <mergeCell ref="M10:Y10"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="B10:J10"/>
-    <mergeCell ref="M7:Y7"/>
-    <mergeCell ref="B9:J9"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="M13:O13"/>
-    <mergeCell ref="M14:O14"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A5">
